--- a/Result/profitability/4934.xlsx
+++ b/Result/profitability/4934.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3650000000000001</v>
+        <v>-0.3375000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-115.3325</v>
+        <v>-114.09375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.96</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05374999999999991</v>
+        <v>0.1924999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-106.8875</v>
+        <v>-85.94875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1612499999999999</v>
+        <v>0.1737499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-89.8325</v>
+        <v>-74.64375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.43</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01624999999999993</v>
+        <v>0.02374999999999994</v>
       </c>
       <c r="N5" t="n">
-        <v>-73.03874999999999</v>
+        <v>-54.235</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05749999999999993</v>
+        <v>0.05749999999999994</v>
       </c>
       <c r="N6" t="n">
-        <v>-47.69125</v>
+        <v>-39.0025</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.63</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1574999999999999</v>
+        <v>0.17125</v>
       </c>
       <c r="N7" t="n">
-        <v>-31.82125</v>
+        <v>-16.77875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2787499999999999</v>
+        <v>0.2824999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.08875</v>
+        <v>-5.220000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5175</v>
+        <v>0.5174999999999998</v>
       </c>
       <c r="N9" t="n">
         <v>1.98875</v>
@@ -1645,10 +1645,10 @@
         <v>2.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7812499999999999</v>
+        <v>0.78125</v>
       </c>
       <c r="N10" t="n">
-        <v>3.892500000000001</v>
+        <v>3.8925</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.5649999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>3.07125</v>
+        <v>3.071249999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -9572,6 +9572,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4934</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>53</v>
+      </c>
+      <c r="D73" t="n">
+        <v>72</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-19</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-35.73</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-104</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-197.27%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>22</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-82</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-37</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-0.3737500000000001</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-120.5</v>
+      </c>
+      <c r="O73" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>1</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X73" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>38.95000000000001</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>-0.5215586502410285</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-0.2608695652173912</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>150.43</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>-0.808068328319725</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
